--- a/assets/multisite-form.xlsx
+++ b/assets/multisite-form.xlsx
@@ -1,636 +1,223 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\OneDrive\바탕 화면\SAP_검수_REV0_260920\3_별첨\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="1" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="7596"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="복수 임시사업장 현황" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="복수,임시사업장" sheetId="1" r:id="rId1"/>
   </sheets>
   <externalReferences>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
+    <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_3월">[1]MASTER!$B$1:$ER$88</definedName>
-    <definedName name="KMAR">[1]MASTER!$B$1:$ER$248</definedName>
-    <definedName name="단위">[2]참고사항!$A$1</definedName>
-    <definedName name="유강">[3]건설신규!#REF!</definedName>
+    <definedName name="_3월">[2]MASTER!$B$1:$ER$88</definedName>
+    <definedName name="KMAR">[2]MASTER!$B$1:$ER$248</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'복수,임시사업장'!$A$1:$N$33</definedName>
+    <definedName name="단위">[3]참고사항!$A$1</definedName>
+    <definedName name="유강" localSheetId="0">[4]건설신규!#REF!</definedName>
+    <definedName name="유강">[4]건설신규!#REF!</definedName>
+    <definedName name="인증번호" localSheetId="0">#REF!</definedName>
     <definedName name="인증번호">#REF!</definedName>
+    <definedName name="인증일" localSheetId="0">#REF!</definedName>
     <definedName name="인증일">#REF!</definedName>
-    <definedName name="유강" localSheetId="0">[3]건설신규!#REF!</definedName>
-    <definedName name="인증번호" localSheetId="0">#REF!</definedName>
-    <definedName name="인증일" localSheetId="0">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'복수 임시사업장 현황'!$A$1:$N$33</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="162913"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+  <si>
+    <t>복수/임시사업장 현황</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>회사명</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>No</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>공사명(임시사업장)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>공사내용
+(현장활동)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>공사기간
+(활동기간)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>공정률
+(%)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>현장위치</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>편도 이동시간
+(본사기준)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>비고</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="@&quot;차&quot;"/>
-    <numFmt numFmtId="165" formatCode="yyyy&quot;년&quot;\ m&quot;월&quot;;@"/>
-    <numFmt numFmtId="166" formatCode="yyyy&quot;년&quot;\ m&quot;월&quot;\ d&quot;일&quot;;@"/>
-  </numFmts>
-  <fonts count="73">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="14">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
+      <family val="2"/>
       <charset val="129"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="8"/>
       <name val="맑은 고딕"/>
+      <family val="2"/>
       <charset val="129"/>
-      <family val="2"/>
-      <sz val="8"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <u/>
+      <sz val="25"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="함초롬바탕"/>
+      <family val="1"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <color theme="1"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="함초롬바탕"/>
+      <family val="1"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <color theme="1"/>
-      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="함초롬바탕"/>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="1"/>
-      <color theme="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="함초롬바탕"/>
+      <b/>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="함초롬바탕"/>
-      <charset val="129"/>
-      <family val="1"/>
-      <color theme="1"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="25"/>
-      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="6"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <sz val="10"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color rgb="FFFF0000"/>
-      <sz val="9"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <sz val="8"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <sz val="7"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <sz val="6"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color rgb="FFFF0000"/>
-      <sz val="8"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="굴림"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <sz val="22"/>
-    </font>
-    <font>
-      <name val="굴림"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="굴림"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="9"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <sz val="8"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <sz val="8"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <sz val="18"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <sz val="9"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <name val="돋움"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <sz val="16"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <sz val="9"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <sz val="25"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FFFF0000"/>
-      <sz val="9"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <color theme="1"/>
-      <sz val="9"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color theme="0"/>
-      <sz val="9"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="2"/>
-      <color theme="10"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="굴림"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <color theme="1"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="굴림"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <color theme="1"/>
-      <sz val="9"/>
-      <u val="single"/>
-    </font>
-    <font>
-      <name val="굴림"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <color theme="1"/>
-      <sz val="8"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color theme="0"/>
-      <sz val="8"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <sz val="7"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color rgb="FFFF0000"/>
-      <sz val="10"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="8"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color theme="8"/>
-      <sz val="8"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color theme="8"/>
-      <sz val="7"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color indexed="81"/>
-      <sz val="8"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF000000"/>
-      <sz val="9"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF000000"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <sz val="8"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color indexed="81"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="돋움"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color indexed="81"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Tahoma"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color indexed="81"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="돋움"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <color indexed="81"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color indexed="81"/>
-      <sz val="9"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <name val="Tahoma"/>
-      <family val="2"/>
-      <color indexed="81"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="2"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="9"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color theme="0"/>
-      <sz val="10"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <sz val="8.5"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color indexed="8"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <sz val="8.5"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color indexed="10"/>
-      <sz val="10"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <color indexed="81"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color indexed="10"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <sz val="10"/>
-      <scheme val="major"/>
-    </font>
   </fonts>
-  <fills count="13">
+  <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.7999816888943144"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.0499893185216834"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.5999938962981048"/>
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -640,49 +227,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.5999938962981048"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.1499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="116">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -694,19 +240,12 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -753,30 +292,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top style="thin">
         <color indexed="64"/>
@@ -796,12 +311,25 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="thin">
+      <top style="thin">
         <color indexed="64"/>
-      </bottom>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -829,86 +357,8 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -916,143 +366,8 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="hair">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1063,134 +378,9 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1207,3536 +397,282 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="double">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="double">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="double">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="double">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="double">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="double">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="10" borderId="0" applyAlignment="1">
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="810">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="53">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="26" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="5" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="21" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="21" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="21" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="29" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="25" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="27" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="27" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="27" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="22" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="22" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="2" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="6" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="33" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="33" fillId="2" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="6" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="22" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="41" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="40" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="21" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="29" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="21" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="71" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="2" borderId="27" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="78" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="79" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="79" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="85" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="86" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="88" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="93" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="94" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="80" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="95" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="96" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="89" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="90" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="81" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="80" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="12" borderId="72" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="12" borderId="73" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="76" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="9" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="9" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="5" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="5" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="5" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="5" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="5" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="71" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="5" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="5" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="5" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="5" borderId="71" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="5" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="66" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="67" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="68" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="45" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="45" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="45" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="39" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="39" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="39" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="5" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="5" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="4" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="17" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="18" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="19" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="25" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="28" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="5" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="5" borderId="21" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="5" borderId="22" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="20" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="21" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="21" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="22" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="23" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="24" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="47" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="48" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="5" borderId="26" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="5" borderId="49" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="5" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="5" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="22" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="22" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="5" borderId="29" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="22" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="21" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="30" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="29" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="20" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="21" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="29" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="21" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="22" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="29" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="31" fillId="2" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="31" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="31" fillId="2" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="33" fillId="2" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="33" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="33" fillId="2" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="22" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="33" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="34" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="35" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="36" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="31" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="37" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="29" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="46" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="23" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="11" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="45" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="16" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="31" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="31" fillId="2" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="26" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="26" fillId="2" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="26" fillId="2" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="38" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="39" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="40" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="41" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="26" fillId="2" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="26" fillId="2" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="26" fillId="2" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="33" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="33" fillId="2" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="31" fillId="5" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="31" fillId="5" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="31" fillId="5" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="45" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="39" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="표준 2" xfId="1"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
-    <cellStyle name="보통" xfId="3" builtinId="28"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="FFFFFF00"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>15240</colOff>
-      <row>0</row>
-      <rowOff>68580</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>847200</colOff>
-      <row>0</row>
-      <rowOff>473525</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="그림 3"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill rotWithShape="1">
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="17911" t="22225" r="17844" b="16392"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>847200</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>473525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="17911" t="22225" r="17844" b="16392"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="15240" y="68580"/>
           <a:ext cx="1152000" cy="404945"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Write"/>
+      <sheetName val="신청서"/>
+      <sheetName val="설문서_공통"/>
+      <sheetName val="추가설문(EO)"/>
+      <sheetName val="추가설문서(ISMS)"/>
+      <sheetName val="추가설문(ABMS)"/>
+      <sheetName val="계약서"/>
+      <sheetName val="복수,임시사업장"/>
+      <sheetName val="전환점검표(Transfer)"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="MASTER"/>
@@ -16194,7 +12130,9 @@
           <cell r="K47" t="str">
             <v>건설, 부동산</v>
           </cell>
-          <cell r="L47" t="str"/>
+          <cell r="L47" t="str">
+            <v/>
+          </cell>
           <cell r="M47" t="str">
             <v>121-747</v>
           </cell>
@@ -22352,7 +18290,9 @@
           <cell r="N73" t="str">
             <v>경기 용인시 역북리 536-1</v>
           </cell>
-          <cell r="P73" t="str"/>
+          <cell r="P73" t="str">
+            <v/>
+          </cell>
           <cell r="R73" t="str">
             <v>가전제품용 타이머 및 소형동기모타에 대한 설계, 개발, 생산 및 부가서비스</v>
           </cell>
@@ -23049,7 +18989,9 @@
           <cell r="N76" t="str">
             <v>경남 마산시 합포구 남성동 247-8</v>
           </cell>
-          <cell r="P76" t="str"/>
+          <cell r="P76" t="str">
+            <v/>
+          </cell>
           <cell r="R76" t="str">
             <v>토목 및 건축공사에 대한 시공 및 부가서비스</v>
           </cell>
@@ -28188,7 +24130,9 @@
           <cell r="BY98">
             <v>37435</v>
           </cell>
-          <cell r="BZ98" t="str"/>
+          <cell r="BZ98" t="str">
+            <v/>
+          </cell>
           <cell r="CA98" t="str">
             <v>김해석</v>
           </cell>
@@ -35916,7 +31860,9 @@
           <cell r="X132" t="str">
             <v>bangjinsa@hanmail.net</v>
           </cell>
-          <cell r="Y132" t="str"/>
+          <cell r="Y132" t="str">
+            <v/>
+          </cell>
           <cell r="Z132" t="str">
             <v>QS 9000/9001</v>
           </cell>
@@ -36911,7 +32857,9 @@
           <cell r="X137" t="str">
             <v>em186540@nuri.net</v>
           </cell>
-          <cell r="Y137" t="str"/>
+          <cell r="Y137" t="str">
+            <v/>
+          </cell>
           <cell r="Z137" t="str">
             <v>ISO 9001:1994</v>
           </cell>
@@ -62227,8 +58175,8 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="전체"/>
@@ -62254,8 +58202,8 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="VXXXXX"/>
@@ -62535,642 +58483,677 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor theme="7" tint="0.7999816888943144"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <tabColor theme="7" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:N33"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col width="2.09765625" customWidth="1" style="791" min="1" max="2"/>
-    <col width="22.5" customWidth="1" style="791" min="3" max="3"/>
-    <col width="10.59765625" customWidth="1" style="791" min="4" max="4"/>
-    <col width="12.3984375" customWidth="1" style="791" min="5" max="5"/>
-    <col width="10" customWidth="1" style="791" min="6" max="6"/>
-    <col width="8.59765625" customWidth="1" style="791" min="7" max="7"/>
-    <col width="2.09765625" customWidth="1" style="791" min="8" max="14"/>
+    <col min="1" max="2" width="2.09765625" customWidth="1"/>
+    <col min="3" max="3" width="22.5" customWidth="1"/>
+    <col min="4" max="4" width="10.59765625" customWidth="1"/>
+    <col min="5" max="5" width="12.3984375" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="8.59765625" customWidth="1"/>
+    <col min="8" max="14" width="2.09765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.35" customHeight="1" s="791">
-      <c r="A1" s="1" t="n"/>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="n"/>
-      <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
-      <c r="N1" s="1" t="n"/>
+    <row r="1" spans="1:14" ht="40.35" customHeight="1">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
     </row>
-    <row r="2" ht="20.1" customHeight="1" s="791">
-      <c r="A2" s="244" t="inlineStr">
-        <is>
-          <t>복수/임시사업장 현황</t>
-        </is>
+    <row r="2" spans="1:14" ht="20.100000000000001" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
       </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
     </row>
-    <row r="3" ht="20.1" customHeight="1" s="791"/>
-    <row r="4" ht="10.35" customFormat="1" customHeight="1" s="6">
-      <c r="A4" s="1" t="n"/>
-      <c r="B4" s="1" t="n"/>
-      <c r="C4" s="1" t="n"/>
-      <c r="D4" s="1" t="n"/>
-      <c r="E4" s="1" t="n"/>
-      <c r="F4" s="1" t="n"/>
-      <c r="G4" s="1" t="n"/>
-      <c r="H4" s="1" t="n"/>
-      <c r="I4" s="1" t="n"/>
-      <c r="J4" s="1" t="n"/>
-      <c r="K4" s="1" t="n"/>
-      <c r="L4" s="1" t="n"/>
-      <c r="M4" s="1" t="n"/>
-      <c r="N4" s="1" t="n"/>
+    <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
     </row>
-    <row r="5" ht="30" customFormat="1" customHeight="1" s="9">
-      <c r="A5" s="224" t="inlineStr">
-        <is>
-          <t>회사명</t>
-        </is>
-      </c>
-      <c r="B5" s="792" t="n"/>
-      <c r="C5" s="793" t="n"/>
-      <c r="D5" s="254" t="n"/>
-      <c r="E5" s="792" t="n"/>
-      <c r="F5" s="792" t="n"/>
-      <c r="G5" s="792" t="n"/>
-      <c r="H5" s="792" t="n"/>
-      <c r="I5" s="792" t="n"/>
-      <c r="J5" s="792" t="n"/>
-      <c r="K5" s="792" t="n"/>
-      <c r="L5" s="792" t="n"/>
-      <c r="M5" s="792" t="n"/>
-      <c r="N5" s="793" t="n"/>
+    <row r="4" spans="1:14" s="3" customFormat="1" ht="10.35" customHeight="1">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
     </row>
-    <row r="6" ht="30" customFormat="1" customHeight="1" s="9">
-      <c r="A6" s="224" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B6" s="793" t="n"/>
-      <c r="C6" s="224" t="inlineStr">
-        <is>
-          <t>공사명(임시사업장)</t>
-        </is>
-      </c>
-      <c r="D6" s="262" t="inlineStr">
-        <is>
-          <t>공사내용
-(현장활동)</t>
-        </is>
-      </c>
-      <c r="E6" s="262" t="inlineStr">
-        <is>
-          <t>공사기간
-(활동기간)</t>
-        </is>
-      </c>
-      <c r="F6" s="262" t="inlineStr">
-        <is>
-          <t>공정률
-(%)</t>
-        </is>
-      </c>
-      <c r="G6" s="262" t="inlineStr">
-        <is>
-          <t>현장위치</t>
-        </is>
-      </c>
-      <c r="H6" s="415" t="inlineStr">
-        <is>
-          <t>편도 이동시간
-(본사기준)</t>
-        </is>
-      </c>
-      <c r="I6" s="792" t="n"/>
-      <c r="J6" s="792" t="n"/>
-      <c r="K6" s="792" t="n"/>
-      <c r="L6" s="793" t="n"/>
-      <c r="M6" s="415" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-      <c r="N6" s="793" t="n"/>
-    </row>
-    <row r="7" ht="24.9" customFormat="1" customHeight="1" s="9">
-      <c r="A7" s="254" t="n">
+    <row r="5" spans="1:14" s="8" customFormat="1" ht="30" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="794" t="n"/>
-      <c r="C7" s="795" t="n"/>
-      <c r="D7" s="796" t="n"/>
-      <c r="E7" s="634" t="n"/>
-      <c r="F7" s="797" t="n"/>
-      <c r="G7" s="798" t="n"/>
-      <c r="H7" s="799" t="n"/>
-      <c r="I7" s="800" t="n"/>
-      <c r="J7" s="800" t="n"/>
-      <c r="K7" s="800" t="n"/>
-      <c r="L7" s="794" t="n"/>
-      <c r="M7" s="801" t="n"/>
-      <c r="N7" s="794" t="n"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="5">
+        <f>[1]Write!C13</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="7"/>
     </row>
-    <row r="8" ht="12" customFormat="1" customHeight="1" s="9">
-      <c r="A8" s="802" t="n"/>
-      <c r="B8" s="803" t="n"/>
-      <c r="C8" s="804" t="n"/>
-      <c r="D8" s="804" t="n"/>
-      <c r="E8" s="635" t="n"/>
-      <c r="F8" s="804" t="n"/>
-      <c r="G8" s="804" t="n"/>
-      <c r="H8" s="802" t="n"/>
-      <c r="L8" s="803" t="n"/>
-      <c r="M8" s="802" t="n"/>
-      <c r="N8" s="803" t="n"/>
-    </row>
-    <row r="9" ht="24.9" customFormat="1" customHeight="1" s="9">
-      <c r="A9" s="805" t="n"/>
-      <c r="B9" s="806" t="n"/>
-      <c r="C9" s="807" t="n"/>
-      <c r="D9" s="807" t="n"/>
-      <c r="E9" s="636" t="n"/>
-      <c r="F9" s="807" t="n"/>
-      <c r="G9" s="807" t="n"/>
-      <c r="H9" s="805" t="n"/>
-      <c r="I9" s="808" t="n"/>
-      <c r="J9" s="808" t="n"/>
-      <c r="K9" s="808" t="n"/>
-      <c r="L9" s="806" t="n"/>
-      <c r="M9" s="805" t="n"/>
-      <c r="N9" s="806" t="n"/>
-    </row>
-    <row r="10" ht="24.9" customFormat="1" customHeight="1" s="9">
-      <c r="A10" s="254" t="n">
+    <row r="6" spans="1:14" s="8" customFormat="1" ht="30" customHeight="1">
+      <c r="A6" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="794" t="n"/>
-      <c r="C10" s="795" t="n"/>
-      <c r="D10" s="796" t="n"/>
-      <c r="E10" s="634" t="n"/>
-      <c r="F10" s="797" t="n"/>
-      <c r="G10" s="798" t="n"/>
-      <c r="H10" s="799" t="n"/>
-      <c r="I10" s="800" t="n"/>
-      <c r="J10" s="800" t="n"/>
-      <c r="K10" s="800" t="n"/>
-      <c r="L10" s="794" t="n"/>
-      <c r="M10" s="801" t="n"/>
-      <c r="N10" s="794" t="n"/>
-    </row>
-    <row r="11" ht="12" customFormat="1" customHeight="1" s="9">
-      <c r="A11" s="802" t="n"/>
-      <c r="B11" s="803" t="n"/>
-      <c r="C11" s="804" t="n"/>
-      <c r="D11" s="804" t="n"/>
-      <c r="E11" s="635" t="n"/>
-      <c r="F11" s="804" t="n"/>
-      <c r="G11" s="804" t="n"/>
-      <c r="H11" s="802" t="n"/>
-      <c r="L11" s="803" t="n"/>
-      <c r="M11" s="802" t="n"/>
-      <c r="N11" s="803" t="n"/>
-    </row>
-    <row r="12" ht="24.9" customFormat="1" customHeight="1" s="9">
-      <c r="A12" s="805" t="n"/>
-      <c r="B12" s="806" t="n"/>
-      <c r="C12" s="807" t="n"/>
-      <c r="D12" s="807" t="n"/>
-      <c r="E12" s="636" t="n"/>
-      <c r="F12" s="807" t="n"/>
-      <c r="G12" s="807" t="n"/>
-      <c r="H12" s="805" t="n"/>
-      <c r="I12" s="808" t="n"/>
-      <c r="J12" s="808" t="n"/>
-      <c r="K12" s="808" t="n"/>
-      <c r="L12" s="806" t="n"/>
-      <c r="M12" s="805" t="n"/>
-      <c r="N12" s="806" t="n"/>
-    </row>
-    <row r="13" ht="24.9" customFormat="1" customHeight="1" s="9">
-      <c r="A13" s="254" t="n">
+      <c r="B6" s="4"/>
+      <c r="C6" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="794" t="n"/>
-      <c r="C13" s="795" t="n"/>
-      <c r="D13" s="796" t="n"/>
-      <c r="E13" s="634" t="n"/>
-      <c r="F13" s="797" t="n"/>
-      <c r="G13" s="798" t="n"/>
-      <c r="H13" s="799" t="n"/>
-      <c r="I13" s="800" t="n"/>
-      <c r="J13" s="800" t="n"/>
-      <c r="K13" s="800" t="n"/>
-      <c r="L13" s="794" t="n"/>
-      <c r="M13" s="801" t="n"/>
-      <c r="N13" s="794" t="n"/>
-    </row>
-    <row r="14" ht="12" customFormat="1" customHeight="1" s="9">
-      <c r="A14" s="802" t="n"/>
-      <c r="B14" s="803" t="n"/>
-      <c r="C14" s="804" t="n"/>
-      <c r="D14" s="804" t="n"/>
-      <c r="E14" s="635" t="n"/>
-      <c r="F14" s="804" t="n"/>
-      <c r="G14" s="804" t="n"/>
-      <c r="H14" s="802" t="n"/>
-      <c r="L14" s="803" t="n"/>
-      <c r="M14" s="802" t="n"/>
-      <c r="N14" s="803" t="n"/>
-    </row>
-    <row r="15" ht="24.9" customFormat="1" customHeight="1" s="9">
-      <c r="A15" s="805" t="n"/>
-      <c r="B15" s="806" t="n"/>
-      <c r="C15" s="807" t="n"/>
-      <c r="D15" s="807" t="n"/>
-      <c r="E15" s="636" t="n"/>
-      <c r="F15" s="807" t="n"/>
-      <c r="G15" s="807" t="n"/>
-      <c r="H15" s="805" t="n"/>
-      <c r="I15" s="808" t="n"/>
-      <c r="J15" s="808" t="n"/>
-      <c r="K15" s="808" t="n"/>
-      <c r="L15" s="806" t="n"/>
-      <c r="M15" s="805" t="n"/>
-      <c r="N15" s="806" t="n"/>
-    </row>
-    <row r="16" ht="24.9" customFormat="1" customHeight="1" s="9">
-      <c r="A16" s="254" t="n">
+      <c r="D6" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="794" t="n"/>
-      <c r="C16" s="795" t="n"/>
-      <c r="D16" s="796" t="n"/>
-      <c r="E16" s="634" t="n"/>
-      <c r="F16" s="809" t="n"/>
-      <c r="G16" s="796" t="n"/>
-      <c r="H16" s="799" t="n"/>
-      <c r="I16" s="800" t="n"/>
-      <c r="J16" s="800" t="n"/>
-      <c r="K16" s="800" t="n"/>
-      <c r="L16" s="794" t="n"/>
-      <c r="M16" s="801" t="n"/>
-      <c r="N16" s="794" t="n"/>
-    </row>
-    <row r="17" ht="12" customFormat="1" customHeight="1" s="9">
-      <c r="A17" s="802" t="n"/>
-      <c r="B17" s="803" t="n"/>
-      <c r="C17" s="804" t="n"/>
-      <c r="D17" s="804" t="n"/>
-      <c r="E17" s="635" t="n"/>
-      <c r="F17" s="804" t="n"/>
-      <c r="G17" s="804" t="n"/>
-      <c r="H17" s="802" t="n"/>
-      <c r="L17" s="803" t="n"/>
-      <c r="M17" s="802" t="n"/>
-      <c r="N17" s="803" t="n"/>
-    </row>
-    <row r="18" ht="24.9" customFormat="1" customHeight="1" s="9">
-      <c r="A18" s="805" t="n"/>
-      <c r="B18" s="806" t="n"/>
-      <c r="C18" s="807" t="n"/>
-      <c r="D18" s="807" t="n"/>
-      <c r="E18" s="636" t="n"/>
-      <c r="F18" s="807" t="n"/>
-      <c r="G18" s="807" t="n"/>
-      <c r="H18" s="805" t="n"/>
-      <c r="I18" s="808" t="n"/>
-      <c r="J18" s="808" t="n"/>
-      <c r="K18" s="808" t="n"/>
-      <c r="L18" s="806" t="n"/>
-      <c r="M18" s="805" t="n"/>
-      <c r="N18" s="806" t="n"/>
-    </row>
-    <row r="19" ht="24.9" customFormat="1" customHeight="1" s="9">
-      <c r="A19" s="254" t="n">
+      <c r="E6" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="794" t="n"/>
-      <c r="C19" s="795" t="n"/>
-      <c r="D19" s="796" t="n"/>
-      <c r="E19" s="634" t="n"/>
-      <c r="F19" s="809" t="n"/>
-      <c r="G19" s="796" t="n"/>
-      <c r="H19" s="799" t="n"/>
-      <c r="I19" s="800" t="n"/>
-      <c r="J19" s="800" t="n"/>
-      <c r="K19" s="800" t="n"/>
-      <c r="L19" s="794" t="n"/>
-      <c r="M19" s="801" t="n"/>
-      <c r="N19" s="794" t="n"/>
-    </row>
-    <row r="20" ht="12" customFormat="1" customHeight="1" s="9">
-      <c r="A20" s="802" t="n"/>
-      <c r="B20" s="803" t="n"/>
-      <c r="C20" s="804" t="n"/>
-      <c r="D20" s="804" t="n"/>
-      <c r="E20" s="635" t="n"/>
-      <c r="F20" s="804" t="n"/>
-      <c r="G20" s="804" t="n"/>
-      <c r="H20" s="802" t="n"/>
-      <c r="L20" s="803" t="n"/>
-      <c r="M20" s="802" t="n"/>
-      <c r="N20" s="803" t="n"/>
-    </row>
-    <row r="21" ht="24.9" customFormat="1" customHeight="1" s="9">
-      <c r="A21" s="805" t="n"/>
-      <c r="B21" s="806" t="n"/>
-      <c r="C21" s="807" t="n"/>
-      <c r="D21" s="807" t="n"/>
-      <c r="E21" s="636" t="n"/>
-      <c r="F21" s="807" t="n"/>
-      <c r="G21" s="807" t="n"/>
-      <c r="H21" s="805" t="n"/>
-      <c r="I21" s="808" t="n"/>
-      <c r="J21" s="808" t="n"/>
-      <c r="K21" s="808" t="n"/>
-      <c r="L21" s="806" t="n"/>
-      <c r="M21" s="805" t="n"/>
-      <c r="N21" s="806" t="n"/>
-    </row>
-    <row r="22" ht="24.9" customFormat="1" customHeight="1" s="9">
-      <c r="A22" s="254" t="n">
+      <c r="F6" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="794" t="n"/>
-      <c r="C22" s="795" t="n"/>
-      <c r="D22" s="796" t="n"/>
-      <c r="E22" s="634" t="n"/>
-      <c r="F22" s="809" t="n"/>
-      <c r="G22" s="796" t="n"/>
-      <c r="H22" s="799" t="n"/>
-      <c r="I22" s="800" t="n"/>
-      <c r="J22" s="800" t="n"/>
-      <c r="K22" s="800" t="n"/>
-      <c r="L22" s="794" t="n"/>
-      <c r="M22" s="801" t="n"/>
-      <c r="N22" s="794" t="n"/>
-    </row>
-    <row r="23" ht="12" customFormat="1" customHeight="1" s="9">
-      <c r="A23" s="802" t="n"/>
-      <c r="B23" s="803" t="n"/>
-      <c r="C23" s="804" t="n"/>
-      <c r="D23" s="804" t="n"/>
-      <c r="E23" s="635" t="n"/>
-      <c r="F23" s="804" t="n"/>
-      <c r="G23" s="804" t="n"/>
-      <c r="H23" s="802" t="n"/>
-      <c r="L23" s="803" t="n"/>
-      <c r="M23" s="802" t="n"/>
-      <c r="N23" s="803" t="n"/>
-    </row>
-    <row r="24" ht="24.9" customFormat="1" customHeight="1" s="9">
-      <c r="A24" s="805" t="n"/>
-      <c r="B24" s="806" t="n"/>
-      <c r="C24" s="807" t="n"/>
-      <c r="D24" s="807" t="n"/>
-      <c r="E24" s="636" t="n"/>
-      <c r="F24" s="807" t="n"/>
-      <c r="G24" s="807" t="n"/>
-      <c r="H24" s="805" t="n"/>
-      <c r="I24" s="808" t="n"/>
-      <c r="J24" s="808" t="n"/>
-      <c r="K24" s="808" t="n"/>
-      <c r="L24" s="806" t="n"/>
-      <c r="M24" s="805" t="n"/>
-      <c r="N24" s="806" t="n"/>
-    </row>
-    <row r="25" ht="24.9" customFormat="1" customHeight="1" s="9">
-      <c r="A25" s="254" t="n">
+      <c r="G6" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="794" t="n"/>
-      <c r="C25" s="795" t="n"/>
-      <c r="D25" s="796" t="n"/>
-      <c r="E25" s="634" t="n"/>
-      <c r="F25" s="809" t="n"/>
-      <c r="G25" s="796" t="n"/>
-      <c r="H25" s="799" t="n"/>
-      <c r="I25" s="800" t="n"/>
-      <c r="J25" s="800" t="n"/>
-      <c r="K25" s="800" t="n"/>
-      <c r="L25" s="794" t="n"/>
-      <c r="M25" s="801" t="n"/>
-      <c r="N25" s="794" t="n"/>
-    </row>
-    <row r="26" ht="12" customFormat="1" customHeight="1" s="9">
-      <c r="A26" s="802" t="n"/>
-      <c r="B26" s="803" t="n"/>
-      <c r="C26" s="804" t="n"/>
-      <c r="D26" s="804" t="n"/>
-      <c r="E26" s="635" t="n"/>
-      <c r="F26" s="804" t="n"/>
-      <c r="G26" s="804" t="n"/>
-      <c r="H26" s="802" t="n"/>
-      <c r="L26" s="803" t="n"/>
-      <c r="M26" s="802" t="n"/>
-      <c r="N26" s="803" t="n"/>
-    </row>
-    <row r="27" ht="24.9" customFormat="1" customHeight="1" s="9">
-      <c r="A27" s="805" t="n"/>
-      <c r="B27" s="806" t="n"/>
-      <c r="C27" s="807" t="n"/>
-      <c r="D27" s="807" t="n"/>
-      <c r="E27" s="636" t="n"/>
-      <c r="F27" s="807" t="n"/>
-      <c r="G27" s="807" t="n"/>
-      <c r="H27" s="805" t="n"/>
-      <c r="I27" s="808" t="n"/>
-      <c r="J27" s="808" t="n"/>
-      <c r="K27" s="808" t="n"/>
-      <c r="L27" s="806" t="n"/>
-      <c r="M27" s="805" t="n"/>
-      <c r="N27" s="806" t="n"/>
-    </row>
-    <row r="28" ht="24.9" customFormat="1" customHeight="1" s="9">
-      <c r="A28" s="254" t="n">
+      <c r="H6" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B28" s="794" t="n"/>
-      <c r="C28" s="795" t="n"/>
-      <c r="D28" s="796" t="n"/>
-      <c r="E28" s="634" t="n"/>
-      <c r="F28" s="809" t="n"/>
-      <c r="G28" s="796" t="n"/>
-      <c r="H28" s="799" t="n"/>
-      <c r="I28" s="800" t="n"/>
-      <c r="J28" s="800" t="n"/>
-      <c r="K28" s="800" t="n"/>
-      <c r="L28" s="794" t="n"/>
-      <c r="M28" s="801" t="n"/>
-      <c r="N28" s="794" t="n"/>
-    </row>
-    <row r="29" ht="12" customFormat="1" customHeight="1" s="9">
-      <c r="A29" s="802" t="n"/>
-      <c r="B29" s="803" t="n"/>
-      <c r="C29" s="804" t="n"/>
-      <c r="D29" s="804" t="n"/>
-      <c r="E29" s="635" t="n"/>
-      <c r="F29" s="804" t="n"/>
-      <c r="G29" s="804" t="n"/>
-      <c r="H29" s="802" t="n"/>
-      <c r="L29" s="803" t="n"/>
-      <c r="M29" s="802" t="n"/>
-      <c r="N29" s="803" t="n"/>
-    </row>
-    <row r="30" ht="24.9" customFormat="1" customHeight="1" s="9">
-      <c r="A30" s="805" t="n"/>
-      <c r="B30" s="806" t="n"/>
-      <c r="C30" s="807" t="n"/>
-      <c r="D30" s="807" t="n"/>
-      <c r="E30" s="636" t="n"/>
-      <c r="F30" s="807" t="n"/>
-      <c r="G30" s="807" t="n"/>
-      <c r="H30" s="805" t="n"/>
-      <c r="I30" s="808" t="n"/>
-      <c r="J30" s="808" t="n"/>
-      <c r="K30" s="808" t="n"/>
-      <c r="L30" s="806" t="n"/>
-      <c r="M30" s="805" t="n"/>
-      <c r="N30" s="806" t="n"/>
-    </row>
-    <row r="31" ht="24.9" customFormat="1" customHeight="1" s="9">
-      <c r="A31" s="254" t="n">
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="794" t="n"/>
-      <c r="C31" s="795" t="n"/>
-      <c r="D31" s="796" t="n"/>
-      <c r="E31" s="634" t="n"/>
-      <c r="F31" s="809" t="n"/>
-      <c r="G31" s="796" t="n"/>
-      <c r="H31" s="799" t="n"/>
-      <c r="I31" s="800" t="n"/>
-      <c r="J31" s="800" t="n"/>
-      <c r="K31" s="800" t="n"/>
-      <c r="L31" s="794" t="n"/>
-      <c r="M31" s="801" t="n"/>
-      <c r="N31" s="794" t="n"/>
+      <c r="N6" s="13"/>
     </row>
-    <row r="32" ht="12" customFormat="1" customHeight="1" s="9">
-      <c r="A32" s="802" t="n"/>
-      <c r="B32" s="803" t="n"/>
-      <c r="C32" s="804" t="n"/>
-      <c r="D32" s="804" t="n"/>
-      <c r="E32" s="635" t="n"/>
-      <c r="F32" s="804" t="n"/>
-      <c r="G32" s="804" t="n"/>
-      <c r="H32" s="802" t="n"/>
-      <c r="L32" s="803" t="n"/>
-      <c r="M32" s="802" t="n"/>
-      <c r="N32" s="803" t="n"/>
+    <row r="7" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A7" s="14">
+        <v>1</v>
+      </c>
+      <c r="B7" s="15"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="20"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="25"/>
     </row>
-    <row r="33" ht="24.9" customFormat="1" customHeight="1" s="9">
-      <c r="A33" s="805" t="n"/>
-      <c r="B33" s="806" t="n"/>
-      <c r="C33" s="807" t="n"/>
-      <c r="D33" s="807" t="n"/>
-      <c r="E33" s="636" t="n"/>
-      <c r="F33" s="807" t="n"/>
-      <c r="G33" s="807" t="n"/>
-      <c r="H33" s="805" t="n"/>
-      <c r="I33" s="808" t="n"/>
-      <c r="J33" s="808" t="n"/>
-      <c r="K33" s="808" t="n"/>
-      <c r="L33" s="806" t="n"/>
-      <c r="M33" s="805" t="n"/>
-      <c r="N33" s="806" t="n"/>
+    <row r="8" spans="1:14" s="8" customFormat="1" ht="12" customHeight="1">
+      <c r="A8" s="26"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="34"/>
+      <c r="L8" s="35"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="37"/>
+    </row>
+    <row r="9" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A9" s="38"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="45"/>
+      <c r="I9" s="46"/>
+      <c r="J9" s="46"/>
+      <c r="K9" s="46"/>
+      <c r="L9" s="47"/>
+      <c r="M9" s="48"/>
+      <c r="N9" s="49"/>
+    </row>
+    <row r="10" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A10" s="14">
+        <v>2</v>
+      </c>
+      <c r="B10" s="15"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="20"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="22"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="24"/>
+      <c r="N10" s="25"/>
+    </row>
+    <row r="11" spans="1:14" s="8" customFormat="1" ht="12" customHeight="1">
+      <c r="A11" s="26"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="34"/>
+      <c r="J11" s="34"/>
+      <c r="K11" s="34"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="37"/>
+    </row>
+    <row r="12" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A12" s="38"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="46"/>
+      <c r="K12" s="46"/>
+      <c r="L12" s="47"/>
+      <c r="M12" s="48"/>
+      <c r="N12" s="49"/>
+    </row>
+    <row r="13" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A13" s="14">
+        <v>3</v>
+      </c>
+      <c r="B13" s="15"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="20"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="23"/>
+      <c r="M13" s="24"/>
+      <c r="N13" s="25"/>
+    </row>
+    <row r="14" spans="1:14" s="8" customFormat="1" ht="12" customHeight="1">
+      <c r="A14" s="26"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="34"/>
+      <c r="J14" s="34"/>
+      <c r="K14" s="34"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="37"/>
+    </row>
+    <row r="15" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A15" s="38"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="46"/>
+      <c r="J15" s="46"/>
+      <c r="K15" s="46"/>
+      <c r="L15" s="47"/>
+      <c r="M15" s="48"/>
+      <c r="N15" s="49"/>
+    </row>
+    <row r="16" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A16" s="14">
+        <v>4</v>
+      </c>
+      <c r="B16" s="15"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="25"/>
+    </row>
+    <row r="17" spans="1:14" s="8" customFormat="1" ht="12" customHeight="1">
+      <c r="A17" s="26"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="51"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="34"/>
+      <c r="K17" s="34"/>
+      <c r="L17" s="35"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="37"/>
+    </row>
+    <row r="18" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A18" s="38"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="52"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="46"/>
+      <c r="J18" s="46"/>
+      <c r="K18" s="46"/>
+      <c r="L18" s="47"/>
+      <c r="M18" s="48"/>
+      <c r="N18" s="49"/>
+    </row>
+    <row r="19" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A19" s="14">
+        <v>5</v>
+      </c>
+      <c r="B19" s="15"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="23"/>
+      <c r="M19" s="24"/>
+      <c r="N19" s="25"/>
+    </row>
+    <row r="20" spans="1:14" s="8" customFormat="1" ht="12" customHeight="1">
+      <c r="A20" s="26"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="34"/>
+      <c r="J20" s="34"/>
+      <c r="K20" s="34"/>
+      <c r="L20" s="35"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="37"/>
+    </row>
+    <row r="21" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A21" s="38"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="52"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="46"/>
+      <c r="J21" s="46"/>
+      <c r="K21" s="46"/>
+      <c r="L21" s="47"/>
+      <c r="M21" s="48"/>
+      <c r="N21" s="49"/>
+    </row>
+    <row r="22" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A22" s="14">
+        <v>6</v>
+      </c>
+      <c r="B22" s="15"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="23"/>
+      <c r="M22" s="24"/>
+      <c r="N22" s="25"/>
+    </row>
+    <row r="23" spans="1:14" s="8" customFormat="1" ht="12" customHeight="1">
+      <c r="A23" s="26"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="33"/>
+      <c r="I23" s="34"/>
+      <c r="J23" s="34"/>
+      <c r="K23" s="34"/>
+      <c r="L23" s="35"/>
+      <c r="M23" s="36"/>
+      <c r="N23" s="37"/>
+    </row>
+    <row r="24" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A24" s="38"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="52"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="46"/>
+      <c r="J24" s="46"/>
+      <c r="K24" s="46"/>
+      <c r="L24" s="47"/>
+      <c r="M24" s="48"/>
+      <c r="N24" s="49"/>
+    </row>
+    <row r="25" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A25" s="14">
+        <v>7</v>
+      </c>
+      <c r="B25" s="15"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="50"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="22"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="23"/>
+      <c r="M25" s="24"/>
+      <c r="N25" s="25"/>
+    </row>
+    <row r="26" spans="1:14" s="8" customFormat="1" ht="12" customHeight="1">
+      <c r="A26" s="26"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="51"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="34"/>
+      <c r="J26" s="34"/>
+      <c r="K26" s="34"/>
+      <c r="L26" s="35"/>
+      <c r="M26" s="36"/>
+      <c r="N26" s="37"/>
+    </row>
+    <row r="27" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A27" s="38"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="46"/>
+      <c r="J27" s="46"/>
+      <c r="K27" s="46"/>
+      <c r="L27" s="47"/>
+      <c r="M27" s="48"/>
+      <c r="N27" s="49"/>
+    </row>
+    <row r="28" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A28" s="14">
+        <v>8</v>
+      </c>
+      <c r="B28" s="15"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="50"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="23"/>
+      <c r="M28" s="24"/>
+      <c r="N28" s="25"/>
+    </row>
+    <row r="29" spans="1:14" s="8" customFormat="1" ht="12" customHeight="1">
+      <c r="A29" s="26"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="51"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="34"/>
+      <c r="J29" s="34"/>
+      <c r="K29" s="34"/>
+      <c r="L29" s="35"/>
+      <c r="M29" s="36"/>
+      <c r="N29" s="37"/>
+    </row>
+    <row r="30" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A30" s="38"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="42"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="41"/>
+      <c r="H30" s="45"/>
+      <c r="I30" s="46"/>
+      <c r="J30" s="46"/>
+      <c r="K30" s="46"/>
+      <c r="L30" s="47"/>
+      <c r="M30" s="48"/>
+      <c r="N30" s="49"/>
+    </row>
+    <row r="31" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A31" s="14">
+        <v>9</v>
+      </c>
+      <c r="B31" s="15"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="50"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="23"/>
+      <c r="M31" s="24"/>
+      <c r="N31" s="25"/>
+    </row>
+    <row r="32" spans="1:14" s="8" customFormat="1" ht="12" customHeight="1">
+      <c r="A32" s="26"/>
+      <c r="B32" s="27"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="51"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="34"/>
+      <c r="J32" s="34"/>
+      <c r="K32" s="34"/>
+      <c r="L32" s="35"/>
+      <c r="M32" s="36"/>
+      <c r="N32" s="37"/>
+    </row>
+    <row r="33" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A33" s="38"/>
+      <c r="B33" s="39"/>
+      <c r="C33" s="40"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="42"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="45"/>
+      <c r="I33" s="46"/>
+      <c r="J33" s="46"/>
+      <c r="K33" s="46"/>
+      <c r="L33" s="47"/>
+      <c r="M33" s="48"/>
+      <c r="N33" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="69">
-    <mergeCell ref="F22:F24"/>
-    <mergeCell ref="A19:B21"/>
-    <mergeCell ref="F13:F15"/>
+    <mergeCell ref="M31:N33"/>
+    <mergeCell ref="A31:B33"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="D31:D33"/>
     <mergeCell ref="F31:F33"/>
-    <mergeCell ref="A10:B12"/>
+    <mergeCell ref="G31:G33"/>
+    <mergeCell ref="H31:L33"/>
+    <mergeCell ref="M25:N27"/>
     <mergeCell ref="A28:B30"/>
-    <mergeCell ref="M19:N21"/>
-    <mergeCell ref="A2:N3"/>
-    <mergeCell ref="A31:B33"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="D28:D30"/>
     <mergeCell ref="F28:F30"/>
+    <mergeCell ref="G28:G30"/>
+    <mergeCell ref="H28:L30"/>
+    <mergeCell ref="M28:N30"/>
+    <mergeCell ref="A25:B27"/>
+    <mergeCell ref="C25:C27"/>
     <mergeCell ref="D25:D27"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="G22:G24"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="H10:L12"/>
-    <mergeCell ref="G31:G33"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="F25:F27"/>
     <mergeCell ref="G25:G27"/>
     <mergeCell ref="H25:L27"/>
-    <mergeCell ref="F10:F12"/>
-    <mergeCell ref="G16:G18"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="H31:L33"/>
+    <mergeCell ref="M19:N21"/>
+    <mergeCell ref="A22:B24"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="F22:F24"/>
+    <mergeCell ref="G22:G24"/>
+    <mergeCell ref="H22:L24"/>
+    <mergeCell ref="M22:N24"/>
+    <mergeCell ref="A19:B21"/>
     <mergeCell ref="C19:C21"/>
-    <mergeCell ref="M10:N12"/>
     <mergeCell ref="D19:D21"/>
     <mergeCell ref="F19:F21"/>
+    <mergeCell ref="G19:G21"/>
+    <mergeCell ref="H19:L21"/>
+    <mergeCell ref="M13:N15"/>
+    <mergeCell ref="A16:B18"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="F16:F18"/>
+    <mergeCell ref="G16:G18"/>
+    <mergeCell ref="H16:L18"/>
+    <mergeCell ref="M16:N18"/>
+    <mergeCell ref="A13:B15"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="F13:F15"/>
+    <mergeCell ref="G13:G15"/>
+    <mergeCell ref="H13:L15"/>
+    <mergeCell ref="M7:N9"/>
+    <mergeCell ref="A10:B12"/>
+    <mergeCell ref="C10:C12"/>
     <mergeCell ref="D10:D12"/>
-    <mergeCell ref="M31:N33"/>
-    <mergeCell ref="A25:B27"/>
+    <mergeCell ref="F10:F12"/>
+    <mergeCell ref="G10:G12"/>
+    <mergeCell ref="H10:L12"/>
+    <mergeCell ref="M10:N12"/>
     <mergeCell ref="A7:B9"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="M22:N24"/>
-    <mergeCell ref="A16:B18"/>
-    <mergeCell ref="M16:N18"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="M7:N9"/>
-    <mergeCell ref="M25:N27"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="F7:F9"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="H7:L9"/>
+    <mergeCell ref="A2:N3"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:N5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="H6:L6"/>
     <mergeCell ref="M6:N6"/>
-    <mergeCell ref="F7:F9"/>
-    <mergeCell ref="F25:F27"/>
-    <mergeCell ref="F16:F18"/>
-    <mergeCell ref="G13:G15"/>
-    <mergeCell ref="M28:N30"/>
-    <mergeCell ref="M13:N15"/>
-    <mergeCell ref="H22:L24"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="H7:L9"/>
-    <mergeCell ref="G10:G12"/>
-    <mergeCell ref="H16:L18"/>
-    <mergeCell ref="C31:C33"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="C25:C27"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="H19:L21"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="G28:G30"/>
-    <mergeCell ref="H28:L30"/>
-    <mergeCell ref="A22:B24"/>
-    <mergeCell ref="G19:G21"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="A13:B15"/>
-    <mergeCell ref="H13:L15"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="D5:N5"/>
-    <mergeCell ref="D28:D30"/>
   </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.5905511811023623" bottom="0.6666666666666666" header="0.3937007874015748" footer="0.3937007874015748"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageMargins left="0.47244094488188981" right="0.47244094488188981" top="0.59055118110236227" bottom="0.66666666666666663" header="0.39370078740157483" footer="0.39370078740157483"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;L&amp;"함초롬돋움,보통"&amp;9 SSR-P-901-01&amp;R&amp;"함초롬돋움,보통"&amp;9 (주)삼성표준인증원</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
+    <oddFooter>&amp;L&amp;"함초롬돋움,보통"&amp;9SSR-P-901-01&amp;R&amp;"함초롬돋움,보통"&amp;9(주)삼성표준인증원</oddFooter>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawingHF r:id="rId3"/>
 </worksheet>
 </file>
--- a/assets/multisite-form.xlsx
+++ b/assets/multisite-form.xlsx
@@ -18,15 +18,14 @@
     <externalReference r:id="rId2"/>
     <externalReference r:id="rId3"/>
     <externalReference r:id="rId4"/>
-    <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_3월">[2]MASTER!$B$1:$ER$88</definedName>
-    <definedName name="KMAR">[2]MASTER!$B$1:$ER$248</definedName>
+    <definedName name="_3월">[1]MASTER!$B$1:$ER$88</definedName>
+    <definedName name="KMAR">[1]MASTER!$B$1:$ER$248</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'복수,임시사업장'!$A$1:$N$33</definedName>
-    <definedName name="단위">[3]참고사항!$A$1</definedName>
-    <definedName name="유강" localSheetId="0">[4]건설신규!#REF!</definedName>
-    <definedName name="유강">[4]건설신규!#REF!</definedName>
+    <definedName name="단위">[2]참고사항!$A$1</definedName>
+    <definedName name="유강" localSheetId="0">[3]건설신규!#REF!</definedName>
+    <definedName name="유강">[3]건설신규!#REF!</definedName>
     <definedName name="인증번호" localSheetId="0">#REF!</definedName>
     <definedName name="인증번호">#REF!</definedName>
     <definedName name="인증일" localSheetId="0">#REF!</definedName>
@@ -418,11 +417,137 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -436,15 +561,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -453,123 +569,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -646,35 +645,6 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
-      <sheetName val="Write"/>
-      <sheetName val="신청서"/>
-      <sheetName val="설문서_공통"/>
-      <sheetName val="추가설문(EO)"/>
-      <sheetName val="추가설문서(ISMS)"/>
-      <sheetName val="추가설문(ABMS)"/>
-      <sheetName val="계약서"/>
-      <sheetName val="복수,임시사업장"/>
-      <sheetName val="전환점검표(Transfer)"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
       <sheetName val="MASTER"/>
       <sheetName val="월별계약추세"/>
       <sheetName val="계약잔고현황"/>
@@ -58175,7 +58145,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -58202,7 +58172,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -58516,40 +58486,40 @@
       <c r="N1" s="1"/>
     </row>
     <row r="2" spans="1:14" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
     </row>
     <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
+      <c r="A3" s="45"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45"/>
     </row>
-    <row r="4" spans="1:14" s="3" customFormat="1" ht="10.35" customHeight="1">
+    <row r="4" spans="1:14" s="2" customFormat="1" ht="10.35" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -58565,524 +58535,562 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
     </row>
-    <row r="5" spans="1:14" s="8" customFormat="1" ht="30" customHeight="1">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:14" s="3" customFormat="1" ht="30" customHeight="1">
+      <c r="A5" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="5">
-        <f>[1]Write!C13</f>
-        <v>0</v>
-      </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="7"/>
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="48"/>
+      <c r="L5" s="48"/>
+      <c r="M5" s="48"/>
+      <c r="N5" s="49"/>
     </row>
-    <row r="6" spans="1:14" s="8" customFormat="1" ht="30" customHeight="1">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:14" s="3" customFormat="1" ht="30" customHeight="1">
+      <c r="A6" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="9" t="s">
+      <c r="B6" s="46"/>
+      <c r="C6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="11" t="s">
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="51"/>
+      <c r="L6" s="52"/>
+      <c r="M6" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="N6" s="13"/>
+      <c r="N6" s="52"/>
     </row>
-    <row r="7" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A7" s="14">
+    <row r="7" spans="1:14" s="3" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A7" s="15">
         <v>1</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="19" t="s">
+      <c r="B7" s="16"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="20"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="23"/>
-      <c r="M7" s="24"/>
-      <c r="N7" s="25"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="32"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="10"/>
     </row>
-    <row r="8" spans="1:14" s="8" customFormat="1" ht="12" customHeight="1">
-      <c r="A8" s="26"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="32"/>
+    <row r="8" spans="1:14" s="3" customFormat="1" ht="12" customHeight="1">
+      <c r="A8" s="17"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="43"/>
       <c r="H8" s="33"/>
       <c r="I8" s="34"/>
       <c r="J8" s="34"/>
       <c r="K8" s="34"/>
       <c r="L8" s="35"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="37"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="12"/>
     </row>
-    <row r="9" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A9" s="38"/>
-      <c r="B9" s="39"/>
-      <c r="C9" s="40"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="43"/>
+    <row r="9" spans="1:14" s="3" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A9" s="19"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="41"/>
       <c r="G9" s="44"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="46"/>
-      <c r="J9" s="46"/>
-      <c r="K9" s="46"/>
-      <c r="L9" s="47"/>
-      <c r="M9" s="48"/>
-      <c r="N9" s="49"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="37"/>
+      <c r="L9" s="38"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="14"/>
     </row>
-    <row r="10" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A10" s="14">
+    <row r="10" spans="1:14" s="3" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A10" s="15">
         <v>2</v>
       </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="19" t="s">
+      <c r="B10" s="16"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="20"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="22"/>
-      <c r="L10" s="23"/>
-      <c r="M10" s="24"/>
-      <c r="N10" s="25"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="10"/>
     </row>
-    <row r="11" spans="1:14" s="8" customFormat="1" ht="12" customHeight="1">
-      <c r="A11" s="26"/>
-      <c r="B11" s="27"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="32"/>
+    <row r="11" spans="1:14" s="3" customFormat="1" ht="12" customHeight="1">
+      <c r="A11" s="17"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="43"/>
       <c r="H11" s="33"/>
       <c r="I11" s="34"/>
       <c r="J11" s="34"/>
       <c r="K11" s="34"/>
       <c r="L11" s="35"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="37"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="12"/>
     </row>
-    <row r="12" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A12" s="38"/>
-      <c r="B12" s="39"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="43"/>
+    <row r="12" spans="1:14" s="3" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A12" s="19"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="41"/>
       <c r="G12" s="44"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="46"/>
-      <c r="J12" s="46"/>
-      <c r="K12" s="46"/>
-      <c r="L12" s="47"/>
-      <c r="M12" s="48"/>
-      <c r="N12" s="49"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="37"/>
+      <c r="J12" s="37"/>
+      <c r="K12" s="37"/>
+      <c r="L12" s="38"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="14"/>
     </row>
-    <row r="13" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A13" s="14">
+    <row r="13" spans="1:14" s="3" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A13" s="15">
         <v>3</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="19" t="s">
+      <c r="B13" s="16"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="20"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="23"/>
-      <c r="M13" s="24"/>
-      <c r="N13" s="25"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31"/>
+      <c r="K13" s="31"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="10"/>
     </row>
-    <row r="14" spans="1:14" s="8" customFormat="1" ht="12" customHeight="1">
-      <c r="A14" s="26"/>
-      <c r="B14" s="27"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="32"/>
+    <row r="14" spans="1:14" s="3" customFormat="1" ht="12" customHeight="1">
+      <c r="A14" s="17"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="43"/>
       <c r="H14" s="33"/>
       <c r="I14" s="34"/>
       <c r="J14" s="34"/>
       <c r="K14" s="34"/>
       <c r="L14" s="35"/>
-      <c r="M14" s="36"/>
-      <c r="N14" s="37"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="12"/>
     </row>
-    <row r="15" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A15" s="38"/>
-      <c r="B15" s="39"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="43"/>
+    <row r="15" spans="1:14" s="3" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A15" s="19"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="41"/>
       <c r="G15" s="44"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="46"/>
-      <c r="K15" s="46"/>
-      <c r="L15" s="47"/>
-      <c r="M15" s="48"/>
-      <c r="N15" s="49"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="37"/>
+      <c r="J15" s="37"/>
+      <c r="K15" s="37"/>
+      <c r="L15" s="38"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="14"/>
     </row>
-    <row r="16" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A16" s="14">
+    <row r="16" spans="1:14" s="3" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A16" s="15">
         <v>4</v>
       </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="24"/>
-      <c r="N16" s="25"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="32"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="10"/>
     </row>
-    <row r="17" spans="1:14" s="8" customFormat="1" ht="12" customHeight="1">
-      <c r="A17" s="26"/>
-      <c r="B17" s="27"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="51"/>
-      <c r="G17" s="29"/>
+    <row r="17" spans="1:14" s="3" customFormat="1" ht="12" customHeight="1">
+      <c r="A17" s="17"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="25"/>
       <c r="H17" s="33"/>
       <c r="I17" s="34"/>
       <c r="J17" s="34"/>
       <c r="K17" s="34"/>
       <c r="L17" s="35"/>
-      <c r="M17" s="36"/>
-      <c r="N17" s="37"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="12"/>
     </row>
-    <row r="18" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A18" s="38"/>
-      <c r="B18" s="39"/>
-      <c r="C18" s="40"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="52"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="46"/>
-      <c r="J18" s="46"/>
-      <c r="K18" s="46"/>
-      <c r="L18" s="47"/>
-      <c r="M18" s="48"/>
-      <c r="N18" s="49"/>
+    <row r="18" spans="1:14" s="3" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A18" s="19"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="37"/>
+      <c r="J18" s="37"/>
+      <c r="K18" s="37"/>
+      <c r="L18" s="38"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="14"/>
     </row>
-    <row r="19" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A19" s="14">
+    <row r="19" spans="1:14" s="3" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A19" s="15">
         <v>5</v>
       </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="22"/>
-      <c r="K19" s="22"/>
-      <c r="L19" s="23"/>
-      <c r="M19" s="24"/>
-      <c r="N19" s="25"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="31"/>
+      <c r="K19" s="31"/>
+      <c r="L19" s="32"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="10"/>
     </row>
-    <row r="20" spans="1:14" s="8" customFormat="1" ht="12" customHeight="1">
-      <c r="A20" s="26"/>
-      <c r="B20" s="27"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="51"/>
-      <c r="G20" s="29"/>
+    <row r="20" spans="1:14" s="3" customFormat="1" ht="12" customHeight="1">
+      <c r="A20" s="17"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="25"/>
       <c r="H20" s="33"/>
       <c r="I20" s="34"/>
       <c r="J20" s="34"/>
       <c r="K20" s="34"/>
       <c r="L20" s="35"/>
-      <c r="M20" s="36"/>
-      <c r="N20" s="37"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="12"/>
     </row>
-    <row r="21" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A21" s="38"/>
-      <c r="B21" s="39"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="52"/>
-      <c r="G21" s="41"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="46"/>
-      <c r="J21" s="46"/>
-      <c r="K21" s="46"/>
-      <c r="L21" s="47"/>
-      <c r="M21" s="48"/>
-      <c r="N21" s="49"/>
+    <row r="21" spans="1:14" s="3" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A21" s="19"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="37"/>
+      <c r="J21" s="37"/>
+      <c r="K21" s="37"/>
+      <c r="L21" s="38"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="14"/>
     </row>
-    <row r="22" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A22" s="14">
+    <row r="22" spans="1:14" s="3" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A22" s="15">
         <v>6</v>
       </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="50"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="23"/>
-      <c r="M22" s="24"/>
-      <c r="N22" s="25"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="32"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="10"/>
     </row>
-    <row r="23" spans="1:14" s="8" customFormat="1" ht="12" customHeight="1">
-      <c r="A23" s="26"/>
-      <c r="B23" s="27"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="51"/>
-      <c r="G23" s="29"/>
+    <row r="23" spans="1:14" s="3" customFormat="1" ht="12" customHeight="1">
+      <c r="A23" s="17"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="25"/>
       <c r="H23" s="33"/>
       <c r="I23" s="34"/>
       <c r="J23" s="34"/>
       <c r="K23" s="34"/>
       <c r="L23" s="35"/>
-      <c r="M23" s="36"/>
-      <c r="N23" s="37"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="12"/>
     </row>
-    <row r="24" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A24" s="38"/>
-      <c r="B24" s="39"/>
-      <c r="C24" s="40"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="52"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="46"/>
-      <c r="K24" s="46"/>
-      <c r="L24" s="47"/>
-      <c r="M24" s="48"/>
-      <c r="N24" s="49"/>
+    <row r="24" spans="1:14" s="3" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A24" s="19"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="37"/>
+      <c r="J24" s="37"/>
+      <c r="K24" s="37"/>
+      <c r="L24" s="38"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="14"/>
     </row>
-    <row r="25" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A25" s="14">
+    <row r="25" spans="1:14" s="3" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A25" s="15">
         <v>7</v>
       </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="21"/>
-      <c r="I25" s="22"/>
-      <c r="J25" s="22"/>
-      <c r="K25" s="22"/>
-      <c r="L25" s="23"/>
-      <c r="M25" s="24"/>
-      <c r="N25" s="25"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="32"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="10"/>
     </row>
-    <row r="26" spans="1:14" s="8" customFormat="1" ht="12" customHeight="1">
-      <c r="A26" s="26"/>
-      <c r="B26" s="27"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="51"/>
-      <c r="G26" s="29"/>
+    <row r="26" spans="1:14" s="3" customFormat="1" ht="12" customHeight="1">
+      <c r="A26" s="17"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="25"/>
       <c r="H26" s="33"/>
       <c r="I26" s="34"/>
       <c r="J26" s="34"/>
       <c r="K26" s="34"/>
       <c r="L26" s="35"/>
-      <c r="M26" s="36"/>
-      <c r="N26" s="37"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="12"/>
     </row>
-    <row r="27" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A27" s="38"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="40"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="52"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="45"/>
-      <c r="I27" s="46"/>
-      <c r="J27" s="46"/>
-      <c r="K27" s="46"/>
-      <c r="L27" s="47"/>
-      <c r="M27" s="48"/>
-      <c r="N27" s="49"/>
+    <row r="27" spans="1:14" s="3" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A27" s="19"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="36"/>
+      <c r="I27" s="37"/>
+      <c r="J27" s="37"/>
+      <c r="K27" s="37"/>
+      <c r="L27" s="38"/>
+      <c r="M27" s="13"/>
+      <c r="N27" s="14"/>
     </row>
-    <row r="28" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A28" s="14">
+    <row r="28" spans="1:14" s="3" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A28" s="15">
         <v>8</v>
       </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="22"/>
-      <c r="J28" s="22"/>
-      <c r="K28" s="22"/>
-      <c r="L28" s="23"/>
-      <c r="M28" s="24"/>
-      <c r="N28" s="25"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="10"/>
     </row>
-    <row r="29" spans="1:14" s="8" customFormat="1" ht="12" customHeight="1">
-      <c r="A29" s="26"/>
-      <c r="B29" s="27"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="51"/>
-      <c r="G29" s="29"/>
+    <row r="29" spans="1:14" s="3" customFormat="1" ht="12" customHeight="1">
+      <c r="A29" s="17"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="25"/>
       <c r="H29" s="33"/>
       <c r="I29" s="34"/>
       <c r="J29" s="34"/>
       <c r="K29" s="34"/>
       <c r="L29" s="35"/>
-      <c r="M29" s="36"/>
-      <c r="N29" s="37"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="12"/>
     </row>
-    <row r="30" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A30" s="38"/>
-      <c r="B30" s="39"/>
-      <c r="C30" s="40"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="42"/>
-      <c r="F30" s="52"/>
-      <c r="G30" s="41"/>
-      <c r="H30" s="45"/>
-      <c r="I30" s="46"/>
-      <c r="J30" s="46"/>
-      <c r="K30" s="46"/>
-      <c r="L30" s="47"/>
-      <c r="M30" s="48"/>
-      <c r="N30" s="49"/>
+    <row r="30" spans="1:14" s="3" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A30" s="19"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="37"/>
+      <c r="J30" s="37"/>
+      <c r="K30" s="37"/>
+      <c r="L30" s="38"/>
+      <c r="M30" s="13"/>
+      <c r="N30" s="14"/>
     </row>
-    <row r="31" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A31" s="14">
+    <row r="31" spans="1:14" s="3" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A31" s="15">
         <v>9</v>
       </c>
-      <c r="B31" s="15"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="21"/>
-      <c r="I31" s="22"/>
-      <c r="J31" s="22"/>
-      <c r="K31" s="22"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="24"/>
-      <c r="N31" s="25"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="24"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="31"/>
+      <c r="J31" s="31"/>
+      <c r="K31" s="31"/>
+      <c r="L31" s="32"/>
+      <c r="M31" s="9"/>
+      <c r="N31" s="10"/>
     </row>
-    <row r="32" spans="1:14" s="8" customFormat="1" ht="12" customHeight="1">
-      <c r="A32" s="26"/>
-      <c r="B32" s="27"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="51"/>
-      <c r="G32" s="29"/>
+    <row r="32" spans="1:14" s="3" customFormat="1" ht="12" customHeight="1">
+      <c r="A32" s="17"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="25"/>
       <c r="H32" s="33"/>
       <c r="I32" s="34"/>
       <c r="J32" s="34"/>
       <c r="K32" s="34"/>
       <c r="L32" s="35"/>
-      <c r="M32" s="36"/>
-      <c r="N32" s="37"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="12"/>
     </row>
-    <row r="33" spans="1:14" s="8" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A33" s="38"/>
-      <c r="B33" s="39"/>
-      <c r="C33" s="40"/>
-      <c r="D33" s="41"/>
-      <c r="E33" s="42"/>
-      <c r="F33" s="52"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="45"/>
-      <c r="I33" s="46"/>
-      <c r="J33" s="46"/>
-      <c r="K33" s="46"/>
-      <c r="L33" s="47"/>
-      <c r="M33" s="48"/>
-      <c r="N33" s="49"/>
+    <row r="33" spans="1:14" s="3" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A33" s="19"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="37"/>
+      <c r="J33" s="37"/>
+      <c r="K33" s="37"/>
+      <c r="L33" s="38"/>
+      <c r="M33" s="13"/>
+      <c r="N33" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="69">
-    <mergeCell ref="M31:N33"/>
-    <mergeCell ref="A31:B33"/>
-    <mergeCell ref="C31:C33"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="F31:F33"/>
-    <mergeCell ref="G31:G33"/>
-    <mergeCell ref="H31:L33"/>
+    <mergeCell ref="A2:N3"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:N5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M7:N9"/>
+    <mergeCell ref="A10:B12"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="F10:F12"/>
+    <mergeCell ref="G10:G12"/>
+    <mergeCell ref="H10:L12"/>
+    <mergeCell ref="M10:N12"/>
+    <mergeCell ref="A7:B9"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="F7:F9"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="H7:L9"/>
+    <mergeCell ref="M13:N15"/>
+    <mergeCell ref="A16:B18"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="F16:F18"/>
+    <mergeCell ref="G16:G18"/>
+    <mergeCell ref="H16:L18"/>
+    <mergeCell ref="M16:N18"/>
+    <mergeCell ref="A13:B15"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="F13:F15"/>
+    <mergeCell ref="G13:G15"/>
+    <mergeCell ref="H13:L15"/>
+    <mergeCell ref="M19:N21"/>
+    <mergeCell ref="A22:B24"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="F22:F24"/>
+    <mergeCell ref="G22:G24"/>
+    <mergeCell ref="H22:L24"/>
+    <mergeCell ref="M22:N24"/>
+    <mergeCell ref="A19:B21"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="F19:F21"/>
+    <mergeCell ref="G19:G21"/>
+    <mergeCell ref="H19:L21"/>
     <mergeCell ref="M25:N27"/>
     <mergeCell ref="A28:B30"/>
     <mergeCell ref="C28:C30"/>
@@ -59097,54 +59105,13 @@
     <mergeCell ref="F25:F27"/>
     <mergeCell ref="G25:G27"/>
     <mergeCell ref="H25:L27"/>
-    <mergeCell ref="M19:N21"/>
-    <mergeCell ref="A22:B24"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="F22:F24"/>
-    <mergeCell ref="G22:G24"/>
-    <mergeCell ref="H22:L24"/>
-    <mergeCell ref="M22:N24"/>
-    <mergeCell ref="A19:B21"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="F19:F21"/>
-    <mergeCell ref="G19:G21"/>
-    <mergeCell ref="H19:L21"/>
-    <mergeCell ref="M13:N15"/>
-    <mergeCell ref="A16:B18"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="F16:F18"/>
-    <mergeCell ref="G16:G18"/>
-    <mergeCell ref="H16:L18"/>
-    <mergeCell ref="M16:N18"/>
-    <mergeCell ref="A13:B15"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="F13:F15"/>
-    <mergeCell ref="G13:G15"/>
-    <mergeCell ref="H13:L15"/>
-    <mergeCell ref="M7:N9"/>
-    <mergeCell ref="A10:B12"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="D10:D12"/>
-    <mergeCell ref="F10:F12"/>
-    <mergeCell ref="G10:G12"/>
-    <mergeCell ref="H10:L12"/>
-    <mergeCell ref="M10:N12"/>
-    <mergeCell ref="A7:B9"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="F7:F9"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="H7:L9"/>
-    <mergeCell ref="A2:N3"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:N5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M31:N33"/>
+    <mergeCell ref="A31:B33"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="F31:F33"/>
+    <mergeCell ref="G31:G33"/>
+    <mergeCell ref="H31:L33"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
